--- a/Kachi_Gun/Table/Config.xlsx
+++ b/Kachi_Gun/Table/Config.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Stage 1-1 (idx=0) 기본 좀비 처치 골드</t>
+          <t>Stage 1-1 (idx=0) 기본 좀비 처치 골드 (10-20 골드 1/2)</t>
         </is>
       </c>
     </row>
@@ -1908,6 +1908,156 @@
       <c r="F47" s="5" t="inlineStr">
         <is>
           <t>던전 수동/AI 분대 이동 속도</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AdGems_Daily</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>회/일</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Shop.xlsx</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>상점 [무료 다이아] 광고 하루 횟수</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AdGems_Amount</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>40</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>다이아</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Shop.xlsx</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>상점 [무료 다이아] 광고 1번에 받는 다이아</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Mission_Gem_Ratio</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>미션</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Mission.xlsx</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>미션 보상(다이아로 친 값) 중 다이아로 주는 비율 — 나머지는 골드</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gem_Gold_Kills</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>마리</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>미션</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mission.xlsx</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>골드 1다이아어치 = 지금 스테이지 좀비 N마리 골드 x 돈 배율 (상점 골드 상자 100다이아 = 600마리와 같은 비율)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Free_Gem_Share</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>밸런스</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>참고값 (게임은 안 읽음): 150챕터까지 무료로 버는 다이아 ÷ 다이아로 살 수 있는 것 전부 = 무료 3 : 결제 7</t>
         </is>
       </c>
     </row>
@@ -2044,13 +2194,13 @@
         <v>10</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.15094</v>
+        <v>1.14887</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>1.02943</v>
+        <v>1.02758</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1.02943</v>
+        <v>1.02758</v>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
@@ -2095,13 +2245,13 @@
         <v>11</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.08189</v>
+        <v>1.08086</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.01551</v>
+        <v>1.01454</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1.01551</v>
+        <v>1.01454</v>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
@@ -2125,7 +2275,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Lv.251 ~ 500</t>
+          <t>Lv.251 ~ 637</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -2146,13 +2296,13 @@
         <v>12</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1.05369</v>
+        <v>1.05303</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.01018</v>
+        <v>1.00954</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.01018</v>
+        <v>1.00954</v>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
@@ -2176,7 +2326,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Lv.501 ~ 1000</t>
+          <t>Lv.638 ~ 1203</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2197,13 +2347,13 @@
         <v>14</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.03615</v>
+        <v>1.03339</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>1.00687</v>
+        <v>1.00419</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1.00687</v>
+        <v>1.00419</v>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
@@ -2227,7 +2377,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Lv.1001 ~ 1500</t>
+          <t>Lv.1204 ~ 1500</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2248,13 +2398,13 @@
         <v>16</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.02684</v>
+        <v>1.02691</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1.00496</v>
+        <v>1.00504</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.00496</v>
+        <v>1.00504</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>

--- a/Kachi_Gun/Table/Config.xlsx
+++ b/Kachi_Gun/Table/Config.xlsx
@@ -2194,13 +2194,13 @@
         <v>10</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.14887</v>
+        <v>1.14714</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>1.02758</v>
+        <v>1.02604</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1.02758</v>
+        <v>1.02604</v>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
@@ -2245,13 +2245,13 @@
         <v>11</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.08086</v>
+        <v>1.08</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.01454</v>
+        <v>1.01374</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1.01454</v>
+        <v>1.01374</v>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Lv.251 ~ 637</t>
+          <t>Lv.251 ~ 625</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -2296,13 +2296,13 @@
         <v>12</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1.05303</v>
+        <v>1.05247</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.00954</v>
+        <v>1.00901</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.00954</v>
+        <v>1.00901</v>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Lv.638 ~ 1203</t>
+          <t>Lv.626 ~ 1222</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2347,13 +2347,13 @@
         <v>14</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.03339</v>
+        <v>1.0341</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>1.00419</v>
+        <v>1.00489</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1.00419</v>
+        <v>1.00489</v>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Lv.1204 ~ 1500</t>
+          <t>Lv.1223 ~ 1500</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2398,13 +2398,13 @@
         <v>16</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.02691</v>
+        <v>1.02703</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1.00504</v>
+        <v>1.00515</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.00504</v>
+        <v>1.00515</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
